--- a/data/flux/paper_code_data/source_data/Fig4_mortality_vs_direction.xlsx
+++ b/data/flux/paper_code_data/source_data/Fig4_mortality_vs_direction.xlsx
@@ -21,7 +21,7 @@
     <t>note</t>
   </si>
   <si>
-    <t>Fig. 4: site maximum of total mortality vs net mortality SHAP (AutoGluon, 24 months); Spearman correlation.</t>
+    <t>Fig. 4: site maximum of relative mortality vs net mortality SHAP (AutoGluon, 24 months); Spearman correlation.</t>
   </si>
   <si>
     <t>SITE_ID</t>
@@ -30,7 +30,7 @@
     <t>response</t>
   </si>
   <si>
-    <t>total_mortality_site_max_pct</t>
+    <t>relative_mortality_site_max_pct</t>
   </si>
   <si>
     <t>net_mortality_shap</t>
